--- a/kaiyi-quotation.xlsx
+++ b/kaiyi-quotation.xlsx
@@ -156,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,10 +187,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -206,7 +205,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -597,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H28"/>
+  <dimension ref="B2:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -628,7 +626,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>QUOTATION  /  2026–2027</t>
+          <t>QUOTATION  ·  2026–2027  ·  RMB</t>
         </is>
       </c>
     </row>
@@ -699,7 +697,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>移动端 H5（Vite + React）+ PC 桌面端响应式适配</t>
+          <t>PC + 移动端 H5（Vite + React，响应式适配）+ Vercel 全球托管</t>
         </is>
       </c>
       <c r="D11" s="7" t="n"/>
@@ -750,7 +748,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>12 个月度主题自动切换 · 3 款相框模板 · 图片生成 · 一键分享</t>
+          <t>12 个月度主题切换 · 3 款相框模板 · 图片生成 · 一键分享</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
@@ -779,12 +777,12 @@
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>文档版本</t>
+          <t>总额</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>V1.1  /  2026-09-08  /  人民币报价 · 含 PC + 移动端</t>
+          <t>人民币 ¥58,000（不含税）/ 含税 ¥61,480</t>
         </is>
       </c>
       <c r="D16" s="7" t="n"/>
@@ -793,72 +791,58 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>设计费结构</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>A 项设计费按月拆解 12 期 · 启动月 ¥3,800 · 月度项 ¥2,200 · 收官月 ¥2,200</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>文档版本</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>V1.3  /  2026-09-08  /  人民币报价</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>报 价 汇 总</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>A. 一次性设计费</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="9">
-        <f>报价明细!E5</f>
-        <v/>
-      </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>B. 一次性开发费</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="9">
-        <f>报价明细!E13</f>
-        <v/>
-      </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>C. 项目管理 / 客户确认</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="9">
-        <f>报价明细!E18</f>
-        <v/>
-      </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>D. 月度维护费（12 个月）</t>
+          <t>A. 设计费（按月拆解 12 期）</t>
         </is>
       </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="9">
-        <f>报价明细!H6</f>
+        <f>报价明细!H15</f>
         <v/>
       </c>
       <c r="G22" s="7" t="n"/>
@@ -867,14 +851,14 @@
     <row r="23" ht="24" customHeight="1">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>E. 托管 / 空间 / 域名（年度）</t>
+          <t>B. 一次性开发费</t>
         </is>
       </c>
       <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="9">
-        <f>报价明细!H11</f>
+        <f>报价明细!H23</f>
         <v/>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -883,14 +867,14 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>F. 运营服务费（年度）</t>
+          <t>C. 客户确认 / 项目管理</t>
         </is>
       </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
       <c r="F24" s="9">
-        <f>报价明细!H15</f>
+        <f>报价明细!H29</f>
         <v/>
       </c>
       <c r="G24" s="7" t="n"/>
@@ -899,80 +883,142 @@
     <row r="25" ht="24" customHeight="1">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>G. 增值税（6%）</t>
+          <t>D. 月度运营与维护</t>
         </is>
       </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="9">
-        <f>报价明细!H19</f>
+        <f>报价明细!H35</f>
         <v/>
       </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>E. 托管 / 域名（年度）</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="9">
+        <f>报价明细!H41</f>
+        <v/>
+      </c>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>F. 运营服务（年度）</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="9">
+        <f>报价明细!H47</f>
+        <v/>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>小计（不含税）</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12">
+        <f>SUM(F22,F23,F24,F25,F26,F27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>G. 增值税（6%）</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="9">
+        <f>ROUND(F28*0.06,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>合计（含税）</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="12">
-        <f>报价明细!H22</f>
-        <v/>
-      </c>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-    </row>
-    <row r="27">
-      <c r="F27" s="13">
-        <f>报价明细!H25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>报价有效期：自本报价单签发之日起 30 个自然日    /    报价单位：人民币元（CNY）    /    含 6% 增值税</t>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12">
+        <f>F28+F29</f>
+        <v/>
+      </c>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>报价有效期：自本报价单签发之日起 30 个自然日    ·    报价单位：人民币元（CNY）    ·    项目年度总额 ¥58,000（不含税）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="F20:H20"/>
+  <mergeCells count="35">
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B20:E20"/>
     <mergeCell ref="C12:H12"/>
+    <mergeCell ref="B20:H20"/>
     <mergeCell ref="F23:H23"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="B4:H4"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B7:H7"/>
+    <mergeCell ref="C17:H17"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="C13:H13"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="F19:H19"/>
     <mergeCell ref="C14:H14"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="B28:E28"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -987,65 +1033,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>工作内容 / 交付物</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>单价 (¥)</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>说明 / 工艺要点</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>计量</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>小计 (¥)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>A. 一次性设计费（Design）</t>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>A. 设计费（Design · 按月拆解 12 期 · 总额 ¥28,000）</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>
@@ -1056,34 +1102,34 @@
       <c r="G2" s="7" t="n"/>
       <c r="H2" s="7" t="n"/>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="17" t="n">
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>主题视觉系统设计</t>
+          <t>9 月（启动月）</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>12 个月主题色板、字体、版式风格指南（Design Guideline）</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="n">
+          <t>品牌视觉系统建立（色板/字体/SVG图标库/PWA图标/风格指南）+ 3 款首发相框模板（路线打卡/旅行明信片/车窗视角）+ PC+移动端双端视觉规范</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>30000</v>
+      <c r="E3" s="17" t="n">
+        <v>3800</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>逐月差异化，确保全年品牌调性一致</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>启动重头，建立全年视觉基底</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H3" s="9">
@@ -1091,34 +1137,34 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="17" t="n">
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>相框模板设计</t>
+          <t>10 月</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>3 款相框 × 12 个月 = 36 款原创版式（路线打卡 / 旅行明信片 / 车窗视角）</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>36</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>1200</v>
+          <t>Autumn Colors 主题色 + 1 款新相框 + 月度文案 + 装饰图标</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>每款含 PC + 移动端双端 3:4 出图样式 + 月度文案 + 装饰图标</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>款</t>
+          <t>逐月新鲜感</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H4" s="9">
@@ -1126,34 +1172,34 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="17" t="n">
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>SVG 图标系统</t>
+          <t>11 月</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>12 个季节 / 主题线性图标（currentColor）</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>600</v>
+          <t>Misty Lake 主题色 + 1 款新相框 + 月度文案 + 装饰图标</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>可在 html2canvas / html-to-image 安全截图</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>个</t>
+          <t>逐月新鲜感</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H5" s="9">
@@ -1161,34 +1207,34 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="17" t="n">
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>PWA 应用图标</t>
+          <t>12 月</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>icon.svg + icon-maskable.svg + 启动画面</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
+          <t>Winter Wonderland 主题色 + 节日专题相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>3000</v>
+      <c r="E6" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>支持添加到主屏幕 / 桌面图标</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>节日营销支持</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H6" s="9">
@@ -1196,34 +1242,34 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="17" t="n">
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>品牌首页 / 任务弹窗视觉</t>
+          <t>1 月</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>首页主视觉 12 套 + 任务弹窗 12 套视觉稿</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>24</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>800</v>
+          <t>New Year Drive 主题色 + 1 款新相框 + 新年文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>PC + 移动端双端布局，含文案层级、按钮态、动效指引</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>新年活动</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H7" s="9">
@@ -1231,65 +1277,139 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="19" t="n"/>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A 小计（一次性设计费）</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="21">
-        <f>SUM(H3:H7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>B. 一次性开发费（Development）</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="17" t="n">
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2 月</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Valentine Ride 主题色 + 情人节专题相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
         <v>1</v>
       </c>
+      <c r="E8" s="17" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>情人节专题</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H8" s="9">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>3 月</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Spring Bloom 主题色 + 春日相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>春日主题</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H9" s="9">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>4 月</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Cherry Road 主题色 + 樱花季专题相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>樱花季专题</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H10" s="9">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="16" t="n">
+        <v>9</v>
+      </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>H5 主框架开发</t>
+          <t>5 月</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Vite + React + PC/移动端响应式适配 + Vercel 全球托管</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
+          <t>Coastal Drift 主题色 + 海岸线相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="18" t="n">
-        <v>25000</v>
+      <c r="E11" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>PC 桌面（≥1024px）+ 移动端（≤768px）双端自适应，PWA Manifest、Service Worker、Lighthouse 95+</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>海岸线主题</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H11" s="9">
@@ -1297,34 +1417,34 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="17" t="n">
-        <v>2</v>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>10</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>四大流程页面</t>
+          <t>6 月</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>品牌首页 / 月度任务弹窗 / 模板创作 / 一键分享</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>4500</v>
+          <t>Desert Light 主题色 + 沙漠光线相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>PC + 移动端双端适配，含路由、状态管理、断点响应式</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>页</t>
+          <t>沙漠光线主题</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H12" s="9">
@@ -1332,34 +1452,34 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="17" t="n">
-        <v>3</v>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="16" t="n">
+        <v>11</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>图片生成与系统分享</t>
+          <t>7 月</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>html-to-image 截图 + Web Share API（带文件）+ FB/IG 面板调起</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
+          <t>Highland Pass 主题色 + 高地穿越相框 + 文案 + 图标</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>12000</v>
+      <c r="E13" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>支持 Facebook / Instagram App 一键带图分享</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>高地穿越 + 半年度回顾</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H13" s="9">
@@ -1367,34 +1487,34 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="17" t="n">
-        <v>4</v>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="16" t="n">
+        <v>12</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>月度主题引擎</t>
+          <t>8 月（收官月）</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>12 个月主题切换 + 全年主题画廊 + 每月差异化文案注入</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
+          <t>Sunset Mile 主题色 + 收官相框 + 文案 + 图标 + 年度专版</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="18" t="n">
-        <v>8000</v>
+      <c r="E14" s="17" t="n">
+        <v>2200</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>数据驱动：themes.js 一处维护全局生效</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>年度收官 + 数据复盘</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H14" s="9">
@@ -1402,100 +1522,100 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>PWA / 缓存 / 离线</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>离线访问、添加到主屏、桌面图标、安装提示</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>A 小计（设计费 · 12 个月度）</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="19">
+        <f>SUM(H3:H14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>B. 一次性开发费（Development）</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>提升海外用户访问体验</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>H5 主框架开发</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Vite + React + PC/移动端响应式适配 + Vercel 全球托管</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>PC 桌面（≥1024px）+ 移动端（≤768px）双端自适应，PWA Manifest、Lighthouse 95+</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>套</t>
         </is>
       </c>
-      <c r="H15" s="9">
-        <f>D15*E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="19" t="n"/>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>B 小计（一次性开发费）</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="21">
-        <f>SUM(H11:H15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>C. 项目管理与客户确认（PM &amp; UAT）</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="H18" s="9">
+        <f>D18*E18</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="17" t="n">
-        <v>1</v>
+      <c r="A19" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>需求梳理 / 方案设计</t>
+          <t>四大流程页面</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>业务调研、用户旅程、信息架构、流程图</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>6000</v>
+          <t>品牌首页 / 月度任务弹窗 / 模板创作 / 一键分享</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>1500</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>输出 PRD / 原型 / 验收标准</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>套</t>
+          <t>PC+移动端双端适配，含路由、状态管理、断点响应式</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>页</t>
         </is>
       </c>
       <c r="H19" s="9">
@@ -1504,33 +1624,33 @@
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="17" t="n">
-        <v>2</v>
+      <c r="A20" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>客户确认 / 版本评审</t>
+          <t>图片生成与系统分享</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>三轮视觉 + 功能评审会（含会议纪要、修订意见落地）</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>3000</v>
+          <t>html-to-image 截图 + Web Share API（带文件）+ FB/IG 调起</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>1000</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>保障上线即验收通过</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>轮</t>
+          <t>支持 Facebook / Instagram App 一键带图分享</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>套</t>
         </is>
       </c>
       <c r="H20" s="9">
@@ -1539,33 +1659,33 @@
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="17" t="n">
-        <v>3</v>
+      <c r="A21" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>UAT 验收与上线</t>
+          <t>月度主题引擎</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>测试用例、回归测试、生产部署、域名备案支持</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="n">
+          <t>12 个月主题切换 + 全年主题画廊 + 每月差异化文案注入</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="18" t="n">
-        <v>6000</v>
+      <c r="E21" s="17" t="n">
+        <v>500</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>覆盖 12 个月度主题上线</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>次</t>
+          <t>数据驱动：themes.js 一处维护全局生效</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>套</t>
         </is>
       </c>
       <c r="H21" s="9">
@@ -1573,100 +1693,100 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>C 小计（项目管理 / 客户确认）</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="21">
-        <f>SUM(H19:H21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>D. 月度维护费（按月续约 · 12 个月）</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="17" t="n">
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>PWA / 缓存 / 离线</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>离线访问、添加到主屏、桌面图标</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>每月新模板设计</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>1 套新相框版式（含 3:4 出图 + 文案 + 图标）</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>保持月度内容新鲜度</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="H25" s="9">
-        <f>D25*E25</f>
-        <v/>
-      </c>
+      <c r="E22" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>提升海外用户访问体验</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="H22" s="9">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>B 小计（一次性开发费）</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="19">
+        <f>SUM(H18:H22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>C. 客户确认与项目管理（UAT &amp; PM）</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="17" t="n">
-        <v>2</v>
+      <c r="A26" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>主题内容更新</t>
+          <t>需求梳理 / 方案确认</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>月度标题、标语、话题标签、品牌色、文案</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>3000</v>
+          <t>需求确认、信息架构、流程图、PRD 验收标准</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>500</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>数据驱动更新 themes.js 一处生效</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
+          <t>覆盖 12 个月度主题上线</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>套</t>
         </is>
       </c>
       <c r="H26" s="9">
@@ -1675,33 +1795,33 @@
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="17" t="n">
-        <v>3</v>
+      <c r="A27" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>上线部署 / 回归</t>
+          <t>客户评审 / 反馈落地</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>新模板上线 + 回归测试 + 旧模板兼容性检查</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>2000</v>
+          <t>两轮视觉 + 功能评审会（含会议纪要、修订意见落地）</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>300</v>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>确保零中断发布</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
+          <t>保障上线即验收通过</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>轮</t>
         </is>
       </c>
       <c r="H27" s="9">
@@ -1709,100 +1829,100 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>D 小计（月度维护 × 12 月）</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="21">
-        <f>SUM(H25:H27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>E. 托管 / 空间 / 域名（年度）</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="17" t="n">
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>UAT 验收与上线支持</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>回归测试、生产部署协助</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Vercel Pro 托管</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>全球 CDN · 自动 HTTPS · 预览部署 · 99.99% SLA</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="n">
+      <c r="E28" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>年度上线支持</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="H28" s="9">
+        <f>D28*E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>C 小计（客户确认 / 项目管理）</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="19">
+        <f>SUM(H26:H28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>D. 月度运营与维护费（按月续约 · 12 个月）</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="18" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>覆盖海外多区域访问</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="H31" s="9">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="17" t="n">
-        <v>2</v>
-      </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>域名注册 / 维护</t>
+          <t>月度主题内容更新</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>.com / .life / .moto 等海外品牌域名</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>500</v>
+          <t>月度文案润色、话题标签、品牌色微调</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>300</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>首年注册 + WHOIS 隐私保护</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>年</t>
+          <t>对应 A 板块每月新模板的文案落地</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H32" s="9">
@@ -1811,33 +1931,33 @@
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="17" t="n">
-        <v>3</v>
+      <c r="A33" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>SSL / DNS 配置</t>
+          <t>上线部署 / 回归测试</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>证书托管 + DNS 解析优化</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>0</v>
+          <t>新版上线、回归测试、兼容性检查、Bug 修复</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>200</v>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Vercel 自动签发，含在托管费内</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>年</t>
+          <t>确保零中断发布，含依赖升级</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="H33" s="9">
@@ -1845,100 +1965,100 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="19" t="n"/>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>E 小计（托管 / 空间 / 域名）</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="21">
-        <f>SUM(H31:H33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>F. 运营服务费（年度）</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="17" t="n">
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>节日 / 营销活动素材</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>节日、营销节点的快速响应素材</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>覆盖 4 个重大节点（圣诞/情人节/樱花季/年度收官）</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="H34" s="9">
+        <f>D34*E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>D 小计（月度运营与维护）</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="19">
+        <f>SUM(H32:H34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>E. 托管 / 空间 / 域名（年度）</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>内容运营支持</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>话题策划、文案润色、多语言适配（含英 / 西 / 阿）</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>覆盖海外三大主要市场</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="H37" s="9">
-        <f>D37*E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="17" t="n">
-        <v>2</v>
-      </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>数据监控 / 月报</t>
+          <t>Vercel Pro 托管</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>UV / 分享率 / 月度活跃 / 转化漏斗 + 报告</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>1500</v>
+          <t>全球 CDN · 自动 HTTPS · 预览部署 · 99.99% SLA</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>1200</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>每月 1 份数据报告 + 优化建议</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>月</t>
+          <t>覆盖海外多区域访问</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>年</t>
         </is>
       </c>
       <c r="H38" s="9">
@@ -1947,33 +2067,33 @@
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="17" t="n">
-        <v>3</v>
+      <c r="A39" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>客户活动支持</t>
+          <t>域名注册 / 维护</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>节日 / 营销节点 / 联合活动素材快速响应</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>3000</v>
+          <t>.com / .life 等海外品牌域名</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>300</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>每季度 1 次专项活动</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>次</t>
+          <t>首年注册 + WHOIS 隐私保护</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>年</t>
         </is>
       </c>
       <c r="H39" s="9">
@@ -1981,55 +2101,226 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="19" t="n"/>
-      <c r="B40" s="20" t="inlineStr">
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>SSL / DNS 配置</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>证书托管 + DNS 解析优化</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Vercel 自动签发，含在托管费内</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="H40" s="9">
+        <f>D40*E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>E 小计（托管 / 空间 / 域名）</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="19">
+        <f>SUM(H38:H40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>F. 运营服务费（年度）</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>内容运营支持</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>话题策划、文案润色</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>服务于月度主题上线</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H44" s="9">
+        <f>D44*E44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>数据监控 / 月报</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>UV / 分享率 / 月度活跃 + 报告</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>每月 1 份数据报告</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="H45" s="9">
+        <f>D45*E45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>客户活动支持</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>节日 / 营销节点快速响应</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>4 次专项活动覆盖</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="H46" s="9">
+        <f>D46*E46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>F 小计（运营服务）</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="21">
-        <f>SUM(H37:H39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>项目总计（含税前 · 不含增值税）</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="n"/>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="23" t="n"/>
-      <c r="G42" s="23" t="n"/>
-      <c r="H42" s="24">
-        <f>H6+H11+H15+H19+H22+H25</f>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="19">
+        <f>SUM(H44:H46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>项目总计（不含税 · 税前）</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="22">
+        <f>H15+H23+H29+H35+H41+H47</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2051,46 +2342,46 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>主题</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>核心话题 / Hashtag</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>相框模板版本</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>上线日期</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
-        <is>
-          <t>维护项</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="17" t="n">
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>设计单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>Share Your Destination</t>
         </is>
@@ -2105,22 +2396,20 @@
           <t>v1.0（首发 3 款）</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>首发上线 + 客户验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="17" t="n">
+      <c r="F2" s="17" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Autumn Colors</t>
         </is>
@@ -2132,25 +2421,23 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>v1.1（新增 1 款）</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>月度新模板 + 主题更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="F3" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Misty Lake</t>
         </is>
@@ -2165,22 +2452,20 @@
           <t>v1.2</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>2026-11-15</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>月度新模板 + 主题更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="17" t="n">
+      <c r="F4" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Winter Wonderland</t>
         </is>
@@ -2195,22 +2480,20 @@
           <t>v1.3</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>节日活动支持</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="17" t="n">
+      <c r="F5" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>New Year Drive</t>
         </is>
@@ -2225,22 +2508,20 @@
           <t>v1.4</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>2027-01-15</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>新年活动专题</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="17" t="n">
+      <c r="F6" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Valentine Ride</t>
         </is>
@@ -2255,22 +2536,20 @@
           <t>v1.5</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>2027-02-14</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>情人节专题</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="17" t="n">
+      <c r="F7" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Spring Bloom</t>
         </is>
@@ -2285,22 +2564,20 @@
           <t>v1.6</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>2027-03-15</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>春日主题</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="17" t="n">
+      <c r="F8" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Cherry Road</t>
         </is>
@@ -2315,22 +2592,20 @@
           <t>v1.7</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>2027-04-15</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>樱花季专题</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="17" t="n">
+      <c r="F9" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Coastal Drift</t>
         </is>
@@ -2345,22 +2620,20 @@
           <t>v1.8</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>2027-05-15</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>海岸线主题</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="17" t="n">
+      <c r="F10" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Desert Light</t>
         </is>
@@ -2375,22 +2648,20 @@
           <t>v1.9</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>2027-06-15</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>沙漠光线主题</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="17" t="n">
+      <c r="F11" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Highland Pass</t>
         </is>
@@ -2405,22 +2676,20 @@
           <t>v2.0</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>2027-07-15</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>高地穿越 + 半年度回顾</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="17" t="n">
+      <c r="F12" s="17" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Sunset Mile</t>
         </is>
@@ -2435,29 +2704,27 @@
           <t>v2.1</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>2027-08-15</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>年度收官 + 数据复盘</t>
-        </is>
+      <c r="F13" s="17" t="n">
+        <v>2200</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>12 个月维护 + 运营 · 小计</t>
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>12 个月 · 设计费小计</t>
         </is>
       </c>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
-      <c r="F15" s="21">
-        <f>报价明细!H19+报价明细!H25</f>
+      <c r="F15" s="19">
+        <f>报价明细!H15</f>
         <v/>
       </c>
     </row>
@@ -2477,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2492,20 +2759,20 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="7" t="n"/>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>条款类别</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>具体内容</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="7" t="n"/>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -2518,165 +2785,191 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="7" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>交付物清单</t>
+          <t>项目总价</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>（1）H5 主程序（含源码，PC + 移动端双端响应式）；（2）12 套主题视觉稿；（3）36 款相框模板；（4）月度维护 12 次；（5）Vercel 全球托管 + 域名；（6）月度数据报告 × 12。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>本项目年度总额 ¥58,000（不含税），含税 ¥61,480。其中设计费占 ¥28,000（按月拆解 12 期）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>一次性付款</t>
+          <t>设计费结构</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>A + B + C 项合计一次性付款 50%，项目启动 5 个工作日内支付；上线验收后 30 日内支付 50% 尾款。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>A 板块设计费按月拆解 12 期：9 月启动月 ¥3,800（含品牌系统基础 + 3 款首发相框），10–8 月月度项 ¥2,200/期，合计 ¥28,000。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>月度付款</t>
+          <t>交付物清单</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>D + F 项按月支付，每月 5 日前开具上月发票并收款；E 项年度费用首次部署时一次性支付。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>（1）H5 主程序（含源码，PC+移动端双端响应式）；（2）12 套主题视觉稿；（3）36 款相框模板；（4）月度维护 12 次；（5）Vercel 全球托管 + 域名；（6）月度数据报告 × 12。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>知识产权</t>
+          <t>一次性付款</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>项目交付物的著作权归乙方所有；甲方拥有本项目专属永久使用权；乙方可在作品集中展示。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>B + C 项合计一次性付款 100%，项目启动 5 个工作日内支付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>客户配合</t>
+          <t>设计费付款</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>甲方应在 5 个工作日内反馈确认意见；超期未反馈视为默认通过确认。每自然月最多发起 2 次模板修订。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+          <t>A 项设计费按月分期付款，每月 5 日前开具上月发票并收款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>维保范围</t>
+          <t>月度付款</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>免费维保期 12 个月，含 Bug 修复、依赖升级、安全补丁；新功能 / 新主题属月度维护范围。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t>D + F 项按月支付，每月 5 日前开具上月发票并收款。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>变更管理</t>
+          <t>年度付款</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>需求变更需双方书面确认；超出原范围的工作量按 1,500 元 / 人天单独计费。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
+          <t>E 项年度费用首次部署时一次性支付。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>数据合规</t>
+          <t>知识产权</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>项目遵守 GDPR 与目标市场数据法规；用户上传图片仅本地处理，不上传服务器。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
+          <t>项目交付物的著作权归乙方所有；甲方拥有本项目专属永久使用权；乙方可在作品集中展示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>终止条款</t>
+          <t>客户配合</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>任意一方可提前 30 日书面通知终止合同；已交付部分按比例结算，未交付部分退还未发生款项。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+          <t>甲方应在 5 个工作日内反馈确认意见；超期未反馈视为默认通过确认。每自然月最多发起 2 次模板修订。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>争议解决</t>
+          <t>维保范围</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>本协议适用中华人民共和国法律；争议提交项目所在地人民法院诉讼解决。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
+          <t>免费维保期 12 个月，含 Bug 修复、依赖升级、安全补丁；新功能 / 新主题属月度维护范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>数据合规</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>项目遵守 GDPR 与目标市场数据法规；用户上传图片仅本地处理，不上传服务器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>终止条款</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>任意一方可提前 30 日书面通知终止合同；已交付部分按比例结算，未交付部分退还未发生款项。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>争议解决</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>本协议适用中华人民共和国法律；争议提交项目所在地人民法院诉讼解决。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
           <t>报价有效期</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>自签发之日起 30 个自然日内有效。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="C8"/>
-    <mergeCell ref="C4"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="C3"/>
-    <mergeCell ref="C12"/>
-    <mergeCell ref="C7"/>
-    <mergeCell ref="C13"/>
-    <mergeCell ref="C11"/>
-    <mergeCell ref="C6"/>
-    <mergeCell ref="C10"/>
-    <mergeCell ref="C2"/>
-    <mergeCell ref="C14"/>
-    <mergeCell ref="C5"/>
-    <mergeCell ref="C9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2709,12 +3002,12 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>委托方（甲方）</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>受托方（乙方）</t>
         </is>
@@ -2831,7 +3124,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>感谢您的信任，期待携手共创 KAIYI 海外品牌新篇章！</t>
         </is>
